--- a/Output Data Tables/APAT Outputs/Aggregated Tables/2021/Airline_Cumulative_Statistics_2021.xlsx
+++ b/Output Data Tables/APAT Outputs/Aggregated Tables/2021/Airline_Cumulative_Statistics_2021.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="36" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="37" uniqueCount="37">
   <si>
     <t>Row</t>
   </si>
@@ -25,6 +25,9 @@
   </si>
   <si>
     <t>American</t>
+  </si>
+  <si>
+    <t>Avelo</t>
   </si>
   <si>
     <t>Breeze</t>
@@ -166,7 +169,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M24"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.42578125" customWidth="true"/>
@@ -189,40 +192,40 @@
         <v>0</v>
       </c>
       <c r="B1" s="0" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C1" s="0" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D1" s="0" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E1" s="0" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F1" s="0" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G1" s="0" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="H1" s="0" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I1" s="0" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="J1" s="0" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="K1" s="0" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="L1" s="0" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="M1" s="0" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="2">
@@ -353,19 +356,19 @@
         <v>4</v>
       </c>
       <c r="B5" s="0">
-        <v>115535801</v>
+        <v>224757511</v>
       </c>
       <c r="C5" s="0">
-        <v>206185838</v>
+        <v>367566255</v>
       </c>
       <c r="D5" s="0">
         <v>0</v>
       </c>
       <c r="E5" s="0">
-        <v>107</v>
+        <v>179</v>
       </c>
       <c r="F5" s="0">
-        <v>3513</v>
+        <v>3132</v>
       </c>
       <c r="G5" s="0">
         <v>0</v>
@@ -374,10 +377,10 @@
         <v>0</v>
       </c>
       <c r="I5" s="0">
-        <v>56.030000000000001</v>
+        <v>61.149999999999999</v>
       </c>
       <c r="J5" s="0">
-        <v>546</v>
+        <v>665</v>
       </c>
       <c r="K5" s="0">
         <v>0</v>
@@ -394,40 +397,40 @@
         <v>5</v>
       </c>
       <c r="B6" s="0">
-        <v>121248228670</v>
+        <v>115535801</v>
       </c>
       <c r="C6" s="0">
-        <v>175431026685</v>
+        <v>206185838</v>
       </c>
       <c r="D6" s="0">
-        <v>620555</v>
+        <v>0</v>
       </c>
       <c r="E6" s="0">
-        <v>171</v>
+        <v>107</v>
       </c>
       <c r="F6" s="0">
-        <v>836374</v>
+        <v>3513</v>
       </c>
       <c r="G6" s="0">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="H6" s="0">
-        <v>8.3000000000000007</v>
+        <v>0</v>
       </c>
       <c r="I6" s="0">
-        <v>69.109999999999999</v>
+        <v>56.030000000000001</v>
       </c>
       <c r="J6" s="0">
-        <v>1111</v>
+        <v>546</v>
       </c>
       <c r="K6" s="0">
-        <v>5432.25</v>
+        <v>0</v>
       </c>
       <c r="L6" s="0">
-        <v>29.460000000000001</v>
+        <v>0</v>
       </c>
       <c r="M6" s="0">
-        <v>0.072999999999999995</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -435,40 +438,40 @@
         <v>6</v>
       </c>
       <c r="B7" s="0">
-        <v>20364786986</v>
+        <v>121248228670</v>
       </c>
       <c r="C7" s="0">
-        <v>26850758906</v>
+        <v>175431026685</v>
       </c>
       <c r="D7" s="0">
-        <v>693281</v>
+        <v>620555</v>
       </c>
       <c r="E7" s="0">
-        <v>193</v>
+        <v>171</v>
       </c>
       <c r="F7" s="0">
-        <v>143467</v>
+        <v>836374</v>
       </c>
       <c r="G7" s="0">
-        <v>3.7000000000000002</v>
+        <v>2.96</v>
       </c>
       <c r="H7" s="0">
-        <v>9.8399999999999999</v>
+        <v>8.3000000000000007</v>
       </c>
       <c r="I7" s="0">
-        <v>75.840000000000003</v>
+        <v>69.109999999999999</v>
       </c>
       <c r="J7" s="0">
-        <v>967</v>
+        <v>1111</v>
       </c>
       <c r="K7" s="0">
-        <v>4474.3100000000004</v>
+        <v>5432.25</v>
       </c>
       <c r="L7" s="0">
-        <v>23.140000000000001</v>
+        <v>29.460000000000001</v>
       </c>
       <c r="M7" s="0">
-        <v>0.063</v>
+        <v>0.072999999999999995</v>
       </c>
     </row>
     <row r="8">
@@ -476,40 +479,40 @@
         <v>7</v>
       </c>
       <c r="B8" s="0">
-        <v>10005093987</v>
+        <v>20364786986</v>
       </c>
       <c r="C8" s="0">
-        <v>14458629851</v>
+        <v>26850758906</v>
       </c>
       <c r="D8" s="0">
-        <v>648951</v>
+        <v>693281</v>
       </c>
       <c r="E8" s="0">
-        <v>164</v>
+        <v>193</v>
       </c>
       <c r="F8" s="0">
-        <v>61368</v>
+        <v>143467</v>
       </c>
       <c r="G8" s="0">
-        <v>2.75</v>
+        <v>3.7000000000000002</v>
       </c>
       <c r="H8" s="0">
-        <v>7</v>
+        <v>9.8399999999999999</v>
       </c>
       <c r="I8" s="0">
-        <v>69.200000000000003</v>
+        <v>75.840000000000003</v>
       </c>
       <c r="J8" s="0">
-        <v>1046</v>
+        <v>967</v>
       </c>
       <c r="K8" s="0">
-        <v>6921.4099999999999</v>
+        <v>4474.3100000000004</v>
       </c>
       <c r="L8" s="0">
-        <v>32.32</v>
+        <v>23.140000000000001</v>
       </c>
       <c r="M8" s="0">
-        <v>0.074999999999999997</v>
+        <v>0.063</v>
       </c>
     </row>
     <row r="9">
@@ -517,37 +520,37 @@
         <v>8</v>
       </c>
       <c r="B9" s="0">
-        <v>41191549602</v>
+        <v>10005093987</v>
       </c>
       <c r="C9" s="0">
-        <v>54165076177</v>
+        <v>14458629851</v>
       </c>
       <c r="D9" s="0">
-        <v>543608</v>
+        <v>648951</v>
       </c>
       <c r="E9" s="0">
-        <v>151</v>
+        <v>164</v>
       </c>
       <c r="F9" s="0">
-        <v>265619</v>
+        <v>61368</v>
       </c>
       <c r="G9" s="0">
-        <v>2.6699999999999999</v>
+        <v>2.75</v>
       </c>
       <c r="H9" s="0">
-        <v>8.6099999999999994</v>
+        <v>7</v>
       </c>
       <c r="I9" s="0">
-        <v>76.049999999999997</v>
+        <v>69.200000000000003</v>
       </c>
       <c r="J9" s="0">
-        <v>1278</v>
+        <v>1046</v>
       </c>
       <c r="K9" s="0">
-        <v>4710.1199999999999</v>
+        <v>6921.4099999999999</v>
       </c>
       <c r="L9" s="0">
-        <v>29.870000000000001</v>
+        <v>32.32</v>
       </c>
       <c r="M9" s="0">
         <v>0.074999999999999997</v>
@@ -558,40 +561,40 @@
         <v>9</v>
       </c>
       <c r="B10" s="0">
-        <v>103581393091</v>
+        <v>41191549602</v>
       </c>
       <c r="C10" s="0">
-        <v>132029420525</v>
+        <v>54165076177</v>
       </c>
       <c r="D10" s="0">
-        <v>495736</v>
+        <v>543608</v>
       </c>
       <c r="E10" s="0">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="F10" s="0">
-        <v>1066596</v>
+        <v>265619</v>
       </c>
       <c r="G10" s="0">
-        <v>4</v>
+        <v>2.6699999999999999</v>
       </c>
       <c r="H10" s="0">
-        <v>8.4499999999999993</v>
+        <v>8.6099999999999994</v>
       </c>
       <c r="I10" s="0">
-        <v>78.450000000000003</v>
+        <v>76.049999999999997</v>
       </c>
       <c r="J10" s="0">
-        <v>791</v>
+        <v>1278</v>
       </c>
       <c r="K10" s="0">
-        <v>4005.04</v>
+        <v>4710.1199999999999</v>
       </c>
       <c r="L10" s="0">
-        <v>25.649999999999999</v>
+        <v>29.870000000000001</v>
       </c>
       <c r="M10" s="0">
-        <v>0.068000000000000005</v>
+        <v>0.074999999999999997</v>
       </c>
     </row>
     <row r="11">
@@ -599,40 +602,40 @@
         <v>10</v>
       </c>
       <c r="B11" s="0">
-        <v>32126066583</v>
+        <v>103581393091</v>
       </c>
       <c r="C11" s="0">
-        <v>40753049115</v>
+        <v>132029420525</v>
       </c>
       <c r="D11" s="0">
-        <v>683317</v>
+        <v>495736</v>
       </c>
       <c r="E11" s="0">
-        <v>187</v>
+        <v>155</v>
       </c>
       <c r="F11" s="0">
-        <v>211779</v>
+        <v>1066596</v>
       </c>
       <c r="G11" s="0">
-        <v>3.5499999999999998</v>
+        <v>4</v>
       </c>
       <c r="H11" s="0">
-        <v>9.6300000000000008</v>
+        <v>8.4499999999999993</v>
       </c>
       <c r="I11" s="0">
-        <v>78.829999999999998</v>
+        <v>78.450000000000003</v>
       </c>
       <c r="J11" s="0">
-        <v>1032</v>
+        <v>791</v>
       </c>
       <c r="K11" s="0">
-        <v>3981.1100000000001</v>
+        <v>4005.04</v>
       </c>
       <c r="L11" s="0">
-        <v>21.34</v>
+        <v>25.649999999999999</v>
       </c>
       <c r="M11" s="0">
-        <v>0.056000000000000001</v>
+        <v>0.068000000000000005</v>
       </c>
     </row>
     <row r="12">
@@ -640,40 +643,40 @@
         <v>11</v>
       </c>
       <c r="B12" s="0">
-        <v>3874332842</v>
+        <v>32126066583</v>
       </c>
       <c r="C12" s="0">
-        <v>5565309602</v>
+        <v>40753049115</v>
       </c>
       <c r="D12" s="0">
-        <v>344388</v>
+        <v>683317</v>
       </c>
       <c r="E12" s="0">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="F12" s="0">
-        <v>25548</v>
+        <v>211779</v>
       </c>
       <c r="G12" s="0">
-        <v>1.5800000000000001</v>
+        <v>3.5499999999999998</v>
       </c>
       <c r="H12" s="0">
-        <v>4.7300000000000004</v>
+        <v>9.6300000000000008</v>
       </c>
       <c r="I12" s="0">
-        <v>69.620000000000005</v>
+        <v>78.829999999999998</v>
       </c>
       <c r="J12" s="0">
-        <v>1191</v>
+        <v>1032</v>
       </c>
       <c r="K12" s="0">
-        <v>4441.1800000000003</v>
+        <v>3981.1100000000001</v>
       </c>
       <c r="L12" s="0">
-        <v>24.260000000000002</v>
+        <v>21.34</v>
       </c>
       <c r="M12" s="0">
-        <v>0.060999999999999999</v>
+        <v>0.056000000000000001</v>
       </c>
     </row>
     <row r="13">
@@ -681,40 +684,40 @@
         <v>12</v>
       </c>
       <c r="B13" s="0">
-        <v>110698392154</v>
+        <v>3874332842</v>
       </c>
       <c r="C13" s="0">
-        <v>155722405468</v>
+        <v>5565309602</v>
       </c>
       <c r="D13" s="0">
-        <v>537771</v>
+        <v>344388</v>
       </c>
       <c r="E13" s="0">
-        <v>172</v>
+        <v>184</v>
       </c>
       <c r="F13" s="0">
-        <v>557940</v>
+        <v>25548</v>
       </c>
       <c r="G13" s="0">
-        <v>1.9299999999999999</v>
+        <v>1.5800000000000001</v>
       </c>
       <c r="H13" s="0">
-        <v>6.7400000000000002</v>
+        <v>4.7300000000000004</v>
       </c>
       <c r="I13" s="0">
-        <v>71.090000000000003</v>
+        <v>69.620000000000005</v>
       </c>
       <c r="J13" s="0">
-        <v>1453</v>
+        <v>1191</v>
       </c>
       <c r="K13" s="0">
-        <v>6424.9700000000003</v>
+        <v>4441.1800000000003</v>
       </c>
       <c r="L13" s="0">
-        <v>34.359999999999999</v>
+        <v>24.260000000000002</v>
       </c>
       <c r="M13" s="0">
-        <v>0.081000000000000003</v>
+        <v>0.060999999999999999</v>
       </c>
     </row>
     <row r="14">
@@ -722,40 +725,40 @@
         <v>13</v>
       </c>
       <c r="B14" s="0">
-        <v>1196165489</v>
+        <v>110698392154</v>
       </c>
       <c r="C14" s="0">
-        <v>1534650900</v>
+        <v>155722405468</v>
       </c>
       <c r="D14" s="0">
-        <v>66320</v>
+        <v>537771</v>
       </c>
       <c r="E14" s="0">
-        <v>50</v>
+        <v>172</v>
       </c>
       <c r="F14" s="0">
-        <v>75877</v>
+        <v>557940</v>
       </c>
       <c r="G14" s="0">
-        <v>3.2799999999999998</v>
+        <v>1.9299999999999999</v>
       </c>
       <c r="H14" s="0">
-        <v>5.1600000000000001</v>
+        <v>6.7400000000000002</v>
       </c>
       <c r="I14" s="0">
-        <v>77.939999999999998</v>
+        <v>71.090000000000003</v>
       </c>
       <c r="J14" s="0">
-        <v>405</v>
+        <v>1453</v>
       </c>
       <c r="K14" s="0">
-        <v>1482.8299999999999</v>
+        <v>6424.9700000000003</v>
       </c>
       <c r="L14" s="0">
-        <v>29.670000000000002</v>
+        <v>34.359999999999999</v>
       </c>
       <c r="M14" s="0">
-        <v>0.115</v>
+        <v>0.081000000000000003</v>
       </c>
     </row>
     <row r="15">
@@ -763,40 +766,40 @@
         <v>14</v>
       </c>
       <c r="B15" s="0">
-        <v>5294154068</v>
+        <v>1196165489</v>
       </c>
       <c r="C15" s="0">
-        <v>7451023804</v>
+        <v>1534650900</v>
       </c>
       <c r="D15" s="0">
-        <v>109978</v>
+        <v>66320</v>
       </c>
       <c r="E15" s="0">
-        <v>67</v>
+        <v>50</v>
       </c>
       <c r="F15" s="0">
-        <v>273236</v>
+        <v>75877</v>
       </c>
       <c r="G15" s="0">
-        <v>4.0300000000000002</v>
+        <v>3.2799999999999998</v>
       </c>
       <c r="H15" s="0">
-        <v>5.7199999999999998</v>
+        <v>5.1600000000000001</v>
       </c>
       <c r="I15" s="0">
-        <v>71.049999999999997</v>
+        <v>77.939999999999998</v>
       </c>
       <c r="J15" s="0">
-        <v>392</v>
+        <v>405</v>
       </c>
       <c r="K15" s="0">
-        <v>1447.1500000000001</v>
+        <v>1482.8299999999999</v>
       </c>
       <c r="L15" s="0">
-        <v>21.09</v>
+        <v>29.670000000000002</v>
       </c>
       <c r="M15" s="0">
-        <v>0.074999999999999997</v>
+        <v>0.115</v>
       </c>
     </row>
     <row r="16">
@@ -804,40 +807,40 @@
         <v>15</v>
       </c>
       <c r="B16" s="0">
-        <v>7341723801</v>
+        <v>5294154068</v>
       </c>
       <c r="C16" s="0">
-        <v>9406748776</v>
+        <v>7451023804</v>
       </c>
       <c r="D16" s="0">
-        <v>54907</v>
+        <v>109978</v>
       </c>
       <c r="E16" s="0">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F16" s="0">
-        <v>264911</v>
+        <v>273236</v>
       </c>
       <c r="G16" s="0">
-        <v>1.55</v>
+        <v>4.0300000000000002</v>
       </c>
       <c r="H16" s="0">
-        <v>2.6899999999999999</v>
+        <v>5.7199999999999998</v>
       </c>
       <c r="I16" s="0">
-        <v>78.049999999999997</v>
+        <v>71.049999999999997</v>
       </c>
       <c r="J16" s="0">
-        <v>510</v>
+        <v>392</v>
       </c>
       <c r="K16" s="0">
-        <v>1597.8599999999999</v>
+        <v>1447.1500000000001</v>
       </c>
       <c r="L16" s="0">
-        <v>23.530000000000001</v>
+        <v>21.09</v>
       </c>
       <c r="M16" s="0">
-        <v>0.078</v>
+        <v>0.074999999999999997</v>
       </c>
     </row>
     <row r="17">
@@ -845,40 +848,40 @@
         <v>16</v>
       </c>
       <c r="B17" s="0">
-        <v>1004554080</v>
+        <v>7379655625</v>
       </c>
       <c r="C17" s="0">
-        <v>1241697900</v>
+        <v>9469022504</v>
       </c>
       <c r="D17" s="0">
-        <v>69137</v>
+        <v>54432</v>
       </c>
       <c r="E17" s="0">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="F17" s="0">
-        <v>59901</v>
+        <v>269871</v>
       </c>
       <c r="G17" s="0">
-        <v>3.3399999999999999</v>
+        <v>1.55</v>
       </c>
       <c r="H17" s="0">
-        <v>5.3499999999999996</v>
+        <v>2.6899999999999999</v>
       </c>
       <c r="I17" s="0">
-        <v>80.900000000000006</v>
+        <v>77.930000000000007</v>
       </c>
       <c r="J17" s="0">
-        <v>415</v>
+        <v>506</v>
       </c>
       <c r="K17" s="0">
-        <v>2045.0999999999999</v>
+        <v>1597.21</v>
       </c>
       <c r="L17" s="0">
-        <v>40.899999999999999</v>
+        <v>23.629999999999999</v>
       </c>
       <c r="M17" s="0">
-        <v>0.158</v>
+        <v>0.079000000000000001</v>
       </c>
     </row>
     <row r="18">
@@ -886,40 +889,40 @@
         <v>17</v>
       </c>
       <c r="B18" s="0">
-        <v>1880416375</v>
+        <v>1004554080</v>
       </c>
       <c r="C18" s="0">
-        <v>2573752996</v>
+        <v>1241697900</v>
       </c>
       <c r="D18" s="0">
-        <v>134470</v>
+        <v>69137</v>
       </c>
       <c r="E18" s="0">
-        <v>76</v>
+        <v>50</v>
       </c>
       <c r="F18" s="0">
-        <v>52793</v>
+        <v>59901</v>
       </c>
       <c r="G18" s="0">
-        <v>2.7599999999999998</v>
+        <v>3.3399999999999999</v>
       </c>
       <c r="H18" s="0">
-        <v>5.2699999999999996</v>
+        <v>5.3499999999999996</v>
       </c>
       <c r="I18" s="0">
-        <v>73.060000000000002</v>
+        <v>80.900000000000006</v>
       </c>
       <c r="J18" s="0">
-        <v>641</v>
+        <v>415</v>
       </c>
       <c r="K18" s="0">
-        <v>886.72000000000003</v>
+        <v>2045.0999999999999</v>
       </c>
       <c r="L18" s="0">
-        <v>11.67</v>
+        <v>40.899999999999999</v>
       </c>
       <c r="M18" s="0">
-        <v>0.035000000000000003</v>
+        <v>0.158</v>
       </c>
     </row>
     <row r="19">
@@ -927,40 +930,40 @@
         <v>18</v>
       </c>
       <c r="B19" s="0">
-        <v>6650609757</v>
+        <v>2811069060</v>
       </c>
       <c r="C19" s="0">
-        <v>8369783759</v>
+        <v>3909087892</v>
       </c>
       <c r="D19" s="0">
-        <v>228495</v>
+        <v>98989</v>
       </c>
       <c r="E19" s="0">
         <v>76</v>
       </c>
       <c r="F19" s="0">
-        <v>166700</v>
+        <v>110754</v>
       </c>
       <c r="G19" s="0">
-        <v>4.5499999999999998</v>
+        <v>2.7999999999999998</v>
       </c>
       <c r="H19" s="0">
-        <v>9.2100000000000009</v>
+        <v>4.46</v>
       </c>
       <c r="I19" s="0">
-        <v>79.459999999999994</v>
+        <v>71.909999999999997</v>
       </c>
       <c r="J19" s="0">
-        <v>664</v>
+        <v>464</v>
       </c>
       <c r="K19" s="0">
-        <v>1199.4300000000001</v>
+        <v>1382.5599999999999</v>
       </c>
       <c r="L19" s="0">
-        <v>15.84</v>
+        <v>18.190000000000001</v>
       </c>
       <c r="M19" s="0">
-        <v>0.048000000000000001</v>
+        <v>0.062</v>
       </c>
     </row>
     <row r="20">
@@ -968,40 +971,40 @@
         <v>19</v>
       </c>
       <c r="B20" s="0">
-        <v>1149052159</v>
+        <v>6650609757</v>
       </c>
       <c r="C20" s="0">
-        <v>1488703295</v>
+        <v>8369783759</v>
       </c>
       <c r="D20" s="0">
-        <v>76698</v>
+        <v>228495</v>
       </c>
       <c r="E20" s="0">
-        <v>50</v>
+        <v>76</v>
       </c>
       <c r="F20" s="0">
-        <v>98988</v>
+        <v>166700</v>
       </c>
       <c r="G20" s="0">
-        <v>5.0999999999999996</v>
+        <v>4.5499999999999998</v>
       </c>
       <c r="H20" s="0">
-        <v>7.2599999999999998</v>
+        <v>9.2100000000000009</v>
       </c>
       <c r="I20" s="0">
-        <v>77.180000000000007</v>
+        <v>79.459999999999994</v>
       </c>
       <c r="J20" s="0">
-        <v>301</v>
+        <v>664</v>
       </c>
       <c r="K20" s="0">
-        <v>1672.22</v>
+        <v>1222.04</v>
       </c>
       <c r="L20" s="0">
-        <v>33.439999999999998</v>
+        <v>16.140000000000001</v>
       </c>
       <c r="M20" s="0">
-        <v>0.158</v>
+        <v>0.049000000000000002</v>
       </c>
     </row>
     <row r="21">
@@ -1009,40 +1012,40 @@
         <v>20</v>
       </c>
       <c r="B21" s="0">
-        <v>5269548743</v>
+        <v>1149052159</v>
       </c>
       <c r="C21" s="0">
-        <v>6710699855</v>
+        <v>1488703295</v>
       </c>
       <c r="D21" s="0">
-        <v>141397</v>
+        <v>76698</v>
       </c>
       <c r="E21" s="0">
-        <v>71</v>
+        <v>50</v>
       </c>
       <c r="F21" s="0">
-        <v>222697</v>
+        <v>98988</v>
       </c>
       <c r="G21" s="0">
-        <v>4.6900000000000004</v>
+        <v>5.0999999999999996</v>
       </c>
       <c r="H21" s="0">
-        <v>7.6399999999999997</v>
+        <v>7.2599999999999998</v>
       </c>
       <c r="I21" s="0">
-        <v>78.519999999999996</v>
+        <v>77.180000000000007</v>
       </c>
       <c r="J21" s="0">
-        <v>422</v>
+        <v>301</v>
       </c>
       <c r="K21" s="0">
-        <v>1831.9300000000001</v>
+        <v>1672.22</v>
       </c>
       <c r="L21" s="0">
-        <v>25.66</v>
+        <v>33.439999999999998</v>
       </c>
       <c r="M21" s="0">
-        <v>0.099000000000000005</v>
+        <v>0.158</v>
       </c>
     </row>
     <row r="22">
@@ -1050,40 +1053,40 @@
         <v>21</v>
       </c>
       <c r="B22" s="0">
-        <v>10070039543</v>
+        <v>5269548743</v>
       </c>
       <c r="C22" s="0">
-        <v>13725688928</v>
+        <v>6710699855</v>
       </c>
       <c r="D22" s="0">
-        <v>166918</v>
+        <v>141397</v>
       </c>
       <c r="E22" s="0">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="F22" s="0">
-        <v>332278</v>
+        <v>222697</v>
       </c>
       <c r="G22" s="0">
-        <v>4.04</v>
+        <v>4.6900000000000004</v>
       </c>
       <c r="H22" s="0">
-        <v>7.6100000000000003</v>
+        <v>7.6399999999999997</v>
       </c>
       <c r="I22" s="0">
-        <v>73.370000000000005</v>
+        <v>78.519999999999996</v>
       </c>
       <c r="J22" s="0">
-        <v>556</v>
+        <v>422</v>
       </c>
       <c r="K22" s="0">
-        <v>1341.3199999999999</v>
+        <v>1831.9300000000001</v>
       </c>
       <c r="L22" s="0">
-        <v>18.059999999999999</v>
+        <v>25.66</v>
       </c>
       <c r="M22" s="0">
-        <v>0.060999999999999999</v>
+        <v>0.099000000000000005</v>
       </c>
     </row>
     <row r="23">
@@ -1091,40 +1094,40 @@
         <v>22</v>
       </c>
       <c r="B23" s="0">
-        <v>20006870329</v>
+        <v>10070039543</v>
       </c>
       <c r="C23" s="0">
-        <v>27037438225</v>
+        <v>13725688928</v>
       </c>
       <c r="D23" s="0">
-        <v>129931</v>
+        <v>166918</v>
       </c>
       <c r="E23" s="0">
-        <v>65</v>
+        <v>74</v>
       </c>
       <c r="F23" s="0">
-        <v>757422</v>
+        <v>332278</v>
       </c>
       <c r="G23" s="0">
-        <v>3.6400000000000001</v>
+        <v>4.04</v>
       </c>
       <c r="H23" s="0">
-        <v>6.4100000000000001</v>
+        <v>7.6100000000000003</v>
       </c>
       <c r="I23" s="0">
-        <v>74</v>
+        <v>73.370000000000005</v>
       </c>
       <c r="J23" s="0">
-        <v>532</v>
+        <v>556</v>
       </c>
       <c r="K23" s="0">
-        <v>1825.8499999999999</v>
+        <v>1341.3199999999999</v>
       </c>
       <c r="L23" s="0">
-        <v>27.460000000000001</v>
+        <v>18.059999999999999</v>
       </c>
       <c r="M23" s="0">
-        <v>0.089999999999999997</v>
+        <v>0.060999999999999999</v>
       </c>
     </row>
     <row r="24">
@@ -1132,39 +1135,80 @@
         <v>23</v>
       </c>
       <c r="B24" s="0">
-        <v>685497794958</v>
+        <v>20006870329</v>
       </c>
       <c r="C24" s="0">
-        <v>929802884475</v>
+        <v>27037438225</v>
       </c>
       <c r="D24" s="0">
-        <v>426163</v>
+        <v>129931</v>
       </c>
       <c r="E24" s="0">
-        <v>133</v>
+        <v>65</v>
       </c>
       <c r="F24" s="0">
-        <v>6655805</v>
+        <v>757422</v>
       </c>
       <c r="G24" s="0">
+        <v>3.6400000000000001</v>
+      </c>
+      <c r="H24" s="0">
+        <v>6.4100000000000001</v>
+      </c>
+      <c r="I24" s="0">
+        <v>74</v>
+      </c>
+      <c r="J24" s="0">
+        <v>532</v>
+      </c>
+      <c r="K24" s="0">
+        <v>1825.8499999999999</v>
+      </c>
+      <c r="L24" s="0">
+        <v>27.460000000000001</v>
+      </c>
+      <c r="M24" s="0">
+        <v>0.089999999999999997</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="0" t="s">
+        <v>24</v>
+      </c>
+      <c r="B25" s="0">
+        <v>686691136978</v>
+      </c>
+      <c r="C25" s="0">
+        <v>931568059354</v>
+      </c>
+      <c r="D25" s="0">
+        <v>422520</v>
+      </c>
+      <c r="E25" s="0">
+        <v>132</v>
+      </c>
+      <c r="F25" s="0">
+        <v>6721858</v>
+      </c>
+      <c r="G25" s="0">
         <v>3.0499999999999998</v>
       </c>
-      <c r="H24" s="0">
-        <v>7.3600000000000003</v>
-      </c>
-      <c r="I24" s="0">
-        <v>73.730000000000004</v>
-      </c>
-      <c r="J24" s="0">
-        <v>886</v>
-      </c>
-      <c r="K24" s="0">
-        <v>4378.2799999999997</v>
-      </c>
-      <c r="L24" s="0">
-        <v>29.27</v>
-      </c>
-      <c r="M24" s="0">
+      <c r="H25" s="0">
+        <v>7.3200000000000003</v>
+      </c>
+      <c r="I25" s="0">
+        <v>73.709999999999994</v>
+      </c>
+      <c r="J25" s="0">
+        <v>880</v>
+      </c>
+      <c r="K25" s="0">
+        <v>4365.1000000000004</v>
+      </c>
+      <c r="L25" s="0">
+        <v>29.260000000000002</v>
+      </c>
+      <c r="M25" s="0">
         <v>0.075999999999999998</v>
       </c>
     </row>

--- a/Output Data Tables/APAT Outputs/Aggregated Tables/2021/Airline_Cumulative_Statistics_2021.xlsx
+++ b/Output Data Tables/APAT Outputs/Aggregated Tables/2021/Airline_Cumulative_Statistics_2021.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="37" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="41" uniqueCount="41">
   <si>
     <t>Row</t>
   </si>
@@ -85,6 +85,18 @@
   </si>
   <si>
     <t>SkyWest</t>
+  </si>
+  <si>
+    <t>FSC</t>
+  </si>
+  <si>
+    <t>Hybrid</t>
+  </si>
+  <si>
+    <t>ULCC</t>
+  </si>
+  <si>
+    <t>Regional</t>
   </si>
   <si>
     <t>All Airlines</t>
@@ -169,7 +181,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M25"/>
+  <dimension ref="A1:M29"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.42578125" customWidth="true"/>
@@ -192,40 +204,40 @@
         <v>0</v>
       </c>
       <c r="B1" s="0" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="C1" s="0" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="D1" s="0" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="E1" s="0" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="F1" s="0" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="G1" s="0" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H1" s="0" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I1" s="0" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J1" s="0" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="K1" s="0" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="L1" s="0" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="M1" s="0" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
     </row>
     <row r="2">
@@ -1176,39 +1188,203 @@
         <v>24</v>
       </c>
       <c r="B25" s="0">
+        <v>368445065181</v>
+      </c>
+      <c r="C25" s="0">
+        <v>513287481483</v>
+      </c>
+      <c r="D25" s="0">
+        <v>584490</v>
+      </c>
+      <c r="E25" s="0">
+        <v>172</v>
+      </c>
+      <c r="F25" s="0">
+        <v>2259253</v>
+      </c>
+      <c r="G25" s="0">
+        <v>2.5699999999999998</v>
+      </c>
+      <c r="H25" s="0">
+        <v>7.8099999999999996</v>
+      </c>
+      <c r="I25" s="0">
+        <v>71.780000000000001</v>
+      </c>
+      <c r="J25" s="0">
+        <v>1210</v>
+      </c>
+      <c r="K25" s="0">
+        <v>6071.3400000000001</v>
+      </c>
+      <c r="L25" s="0">
+        <v>33.100000000000001</v>
+      </c>
+      <c r="M25" s="0">
+        <v>0.081000000000000003</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="B26" s="0">
+        <v>188649852088</v>
+      </c>
+      <c r="C26" s="0">
+        <v>246601789565</v>
+      </c>
+      <c r="D26" s="0">
+        <v>538009</v>
+      </c>
+      <c r="E26" s="0">
+        <v>156</v>
+      </c>
+      <c r="F26" s="0">
+        <v>1597769</v>
+      </c>
+      <c r="G26" s="0">
+        <v>3.4900000000000002</v>
+      </c>
+      <c r="H26" s="0">
+        <v>8.6099999999999994</v>
+      </c>
+      <c r="I26" s="0">
+        <v>76.5</v>
+      </c>
+      <c r="J26" s="0">
+        <v>952</v>
+      </c>
+      <c r="K26" s="0">
+        <v>4300.6400000000003</v>
+      </c>
+      <c r="L26" s="0">
+        <v>26.75</v>
+      </c>
+      <c r="M26" s="0">
+        <v>0.069000000000000006</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="0" t="s">
+        <v>26</v>
+      </c>
+      <c r="B27" s="0">
+        <v>68764500856</v>
+      </c>
+      <c r="C27" s="0">
+        <v>90740991244</v>
+      </c>
+      <c r="D27" s="0">
+        <v>596470</v>
+      </c>
+      <c r="E27" s="0">
+        <v>185</v>
+      </c>
+      <c r="F27" s="0">
+        <v>497112</v>
+      </c>
+      <c r="G27" s="0">
+        <v>3.27</v>
+      </c>
+      <c r="H27" s="0">
+        <v>8.5199999999999996</v>
+      </c>
+      <c r="I27" s="0">
+        <v>75.780000000000001</v>
+      </c>
+      <c r="J27" s="0">
+        <v>982</v>
+      </c>
+      <c r="K27" s="0">
+        <v>4140.0799999999999</v>
+      </c>
+      <c r="L27" s="0">
+        <v>22.27</v>
+      </c>
+      <c r="M27" s="0">
+        <v>0.058999999999999997</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="0" t="s">
+        <v>27</v>
+      </c>
+      <c r="B28" s="0">
+        <v>60831718853</v>
+      </c>
+      <c r="C28" s="0">
+        <v>80937797062</v>
+      </c>
+      <c r="D28" s="0">
+        <v>113023</v>
+      </c>
+      <c r="E28" s="0">
+        <v>67</v>
+      </c>
+      <c r="F28" s="0">
+        <v>2367724</v>
+      </c>
+      <c r="G28" s="0">
+        <v>3.3100000000000001</v>
+      </c>
+      <c r="H28" s="0">
+        <v>5.6500000000000004</v>
+      </c>
+      <c r="I28" s="0">
+        <v>75.159999999999997</v>
+      </c>
+      <c r="J28" s="0">
+        <v>495</v>
+      </c>
+      <c r="K28" s="0">
+        <v>1608.8399999999999</v>
+      </c>
+      <c r="L28" s="0">
+        <v>23.59</v>
+      </c>
+      <c r="M28" s="0">
+        <v>0.080000000000000002</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="B29" s="0">
         <v>686691136978</v>
       </c>
-      <c r="C25" s="0">
+      <c r="C29" s="0">
         <v>931568059354</v>
       </c>
-      <c r="D25" s="0">
+      <c r="D29" s="0">
         <v>422520</v>
       </c>
-      <c r="E25" s="0">
+      <c r="E29" s="0">
         <v>132</v>
       </c>
-      <c r="F25" s="0">
+      <c r="F29" s="0">
         <v>6721858</v>
       </c>
-      <c r="G25" s="0">
+      <c r="G29" s="0">
         <v>3.0499999999999998</v>
       </c>
-      <c r="H25" s="0">
+      <c r="H29" s="0">
         <v>7.3200000000000003</v>
       </c>
-      <c r="I25" s="0">
+      <c r="I29" s="0">
         <v>73.709999999999994</v>
       </c>
-      <c r="J25" s="0">
+      <c r="J29" s="0">
         <v>880</v>
       </c>
-      <c r="K25" s="0">
+      <c r="K29" s="0">
         <v>4365.1000000000004</v>
       </c>
-      <c r="L25" s="0">
+      <c r="L29" s="0">
         <v>29.260000000000002</v>
       </c>
-      <c r="M25" s="0">
+      <c r="M29" s="0">
         <v>0.075999999999999998</v>
       </c>
     </row>
